--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,6 +2166,126 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118858021</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555068</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6343405</v>
+      </c>
+      <c r="S14" t="n">
+        <v>228</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38316160</v>
+        <v>118922019</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>108714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555068.1351438325</v>
+        <v>555459</v>
       </c>
       <c r="R2" t="n">
-        <v>6343405.318125473</v>
+        <v>6343786</v>
       </c>
       <c r="S2" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:10</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Grustaget</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicklas Strömberg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicklas Strömberg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38330565</v>
+        <v>118922017</v>
       </c>
       <c r="B3" t="n">
-        <v>57007</v>
+        <v>108714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,50 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555068.1351438325</v>
+        <v>555564</v>
       </c>
       <c r="R3" t="n">
-        <v>6343405.318125473</v>
+        <v>6343805</v>
       </c>
       <c r="S3" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:10</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Grustaget</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Strömberg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Strömberg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>42558532</v>
+        <v>118922049</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
+        <v>104901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,55 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555068.1351438325</v>
+        <v>555461</v>
       </c>
       <c r="R4" t="n">
-        <v>6343405.318125473</v>
+        <v>6343872</v>
       </c>
       <c r="S4" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,27 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-05-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Intressant uppgörelse mellan två hannar</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,26 +965,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bill Andersson, Mariette Persson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42521434</v>
+        <v>118922128</v>
       </c>
       <c r="B5" t="n">
-        <v>56632</v>
+        <v>106120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,51 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555068.1351438325</v>
+        <v>555457</v>
       </c>
       <c r="R5" t="n">
-        <v>6343405.318125473</v>
+        <v>6343871</v>
       </c>
       <c r="S5" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-05-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-05-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Calle Ljungberg</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Calle Ljungberg, Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>43334929</v>
+        <v>118922018</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
+        <v>108714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,46 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555068.1351438325</v>
+        <v>555849</v>
       </c>
       <c r="R6" t="n">
-        <v>6343405.318125473</v>
+        <v>6343838</v>
       </c>
       <c r="S6" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-07-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-07-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43700438</v>
+        <v>118922016</v>
       </c>
       <c r="B7" t="n">
-        <v>56806</v>
+        <v>108714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,41 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555068.1351438325</v>
+        <v>555502</v>
       </c>
       <c r="R7" t="n">
-        <v>6343405.318125473</v>
+        <v>6343851</v>
       </c>
       <c r="S7" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,22 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45037704</v>
+        <v>118922127</v>
       </c>
       <c r="B8" t="n">
-        <v>56355</v>
+        <v>106120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,41 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102975</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555068.1351438325</v>
+        <v>555417</v>
       </c>
       <c r="R8" t="n">
-        <v>6343405.318125473</v>
+        <v>6343871</v>
       </c>
       <c r="S8" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,27 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1977-05-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1977-05-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>års-X</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Willy Strömblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Willy Strömblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47191927</v>
+        <v>38316160</v>
       </c>
       <c r="B9" t="n">
-        <v>56812</v>
+        <v>57064</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,16 +1410,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1577,12 +1429,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sträckande O</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1621,22 +1473,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1981-04-12</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1981-04-12</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Grustaget</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,22 +1508,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Willy Strömblad</t>
+          <t>Nicklas Strömberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Willy Strömblad</t>
+          <t>Nicklas Strömberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69204987</v>
+        <v>38330565</v>
       </c>
       <c r="B10" t="n">
-        <v>98536</v>
+        <v>57007</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1679,52 +1536,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1853</v>
+        <v>103042</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen, Sm</t>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555681.7494332279</v>
+        <v>555068.1351438325</v>
       </c>
       <c r="R10" t="n">
-        <v>6343473.666202914</v>
+        <v>6343405.318125473</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1599,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1999-05-02</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1999-05-02</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Grustaget</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,76 +1634,79 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Willy Strömblad</t>
+          <t>Nicklas Strömberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Willy Strömblad, Birgitta Strömblad</t>
+          <t>Nicklas Strömberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53309028</v>
+        <v>42558532</v>
       </c>
       <c r="B11" t="n">
-        <v>98536</v>
+        <v>56411</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1853</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slätmon, ost, Sm</t>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554921.6844280366</v>
+        <v>555068.1351438325</v>
       </c>
       <c r="R11" t="n">
-        <v>6343364.925492699</v>
+        <v>6343405.318125473</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1871,27 +1730,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2012-05-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-12-31</t>
+          <t>2012-05-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Observatör: Thomas Tege Gustafsson</t>
+          <t>Intressant uppgörelse mellan två hannar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,26 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Bill Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Bill Andersson, Mariette Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73983133</v>
+        <v>42521434</v>
       </c>
       <c r="B12" t="n">
-        <v>106707</v>
+        <v>56632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,37 +1793,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220204</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30 Slätmon 650m NNV Forsaryds gård, Sm</t>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554960.43416335</v>
+        <v>555068.1351438325</v>
       </c>
       <c r="R12" t="n">
-        <v>6343306.437132297</v>
+        <v>6343405.318125473</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1992,27 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>2012-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>2012-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5G8b 4813. SOM: Hypochoeris maculata. LEG: Göran Wendt, Allan Nicklasson</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,35 +1887,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallhed</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Calle Ljungberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Calle Ljungberg, Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89873029</v>
+        <v>43334929</v>
       </c>
       <c r="B13" t="n">
-        <v>56286</v>
+        <v>56540</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2064,32 +1919,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
@@ -2126,22 +1982,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2012-07-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2012-07-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118858021</v>
+        <v>43700438</v>
       </c>
       <c r="B14" t="n">
-        <v>57443</v>
+        <v>56806</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2184,42 +2040,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555068</v>
+        <v>555068.1351438325</v>
       </c>
       <c r="R14" t="n">
-        <v>6343405</v>
+        <v>6343405.318125473</v>
       </c>
       <c r="S14" t="n">
         <v>228</v>
@@ -2246,22 +2098,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2285,6 +2137,1082 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>45037704</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56355</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555068.1351438325</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6343405.318125473</v>
+      </c>
+      <c r="S15" t="n">
+        <v>228</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1977-05-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1977-05-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>års-X</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Willy Strömblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Willy Strömblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>47191927</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56812</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>sträckande O</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555068.1351438325</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6343405.318125473</v>
+      </c>
+      <c r="S16" t="n">
+        <v>228</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1981-04-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1981-04-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Willy Strömblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Willy Strömblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>69204987</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98536</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555681.7494332279</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6343473.666202914</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1999-05-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1999-05-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Willy Strömblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Willy Strömblad, Birgitta Strömblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>53309028</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98536</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slätmon, ost, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>554921.6844280366</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6343364.925492699</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2011-12-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observatör: Thomas Tege Gustafsson</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73983133</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106707</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>30 Slätmon 650m NNV Forsaryds gård, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>554960.43416335</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6343306.437132297</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5G8b 4813. SOM: Hypochoeris maculata. LEG: Göran Wendt, Allan Nicklasson</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Tallhed</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89873029</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56286</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555068.1351438325</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6343405.318125473</v>
+      </c>
+      <c r="S20" t="n">
+        <v>228</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118858021</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555068</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6343405</v>
+      </c>
+      <c r="S21" t="n">
+        <v>228</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118922021</v>
+      </c>
+      <c r="B22" t="n">
+        <v>108714</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Moråns ravin, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555154</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6343774</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118922042</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106569</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Moråns ravin, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555114</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6343763</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118922019</v>
+        <v>118922017</v>
       </c>
       <c r="B2" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555459</v>
+        <v>555564</v>
       </c>
       <c r="R2" t="n">
-        <v>6343786</v>
+        <v>6343805</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922017</v>
+        <v>118922016</v>
       </c>
       <c r="B3" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555564</v>
+        <v>555502</v>
       </c>
       <c r="R3" t="n">
-        <v>6343805</v>
+        <v>6343851</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,7 +882,7 @@
         <v>118922049</v>
       </c>
       <c r="B4" t="n">
-        <v>104901</v>
+        <v>104908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118922128</v>
+        <v>118922019</v>
       </c>
       <c r="B5" t="n">
-        <v>106120</v>
+        <v>108721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555457</v>
+        <v>555459</v>
       </c>
       <c r="R5" t="n">
-        <v>6343871</v>
+        <v>6343786</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118922018</v>
+        <v>118922128</v>
       </c>
       <c r="B6" t="n">
-        <v>108714</v>
+        <v>106127</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555849</v>
+        <v>555457</v>
       </c>
       <c r="R6" t="n">
-        <v>6343838</v>
+        <v>6343871</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118922016</v>
+        <v>118922127</v>
       </c>
       <c r="B7" t="n">
-        <v>108714</v>
+        <v>106127</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555502</v>
+        <v>555417</v>
       </c>
       <c r="R7" t="n">
-        <v>6343851</v>
+        <v>6343871</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118922127</v>
+        <v>118922018</v>
       </c>
       <c r="B8" t="n">
-        <v>106120</v>
+        <v>108721</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555417</v>
+        <v>555849</v>
       </c>
       <c r="R8" t="n">
-        <v>6343871</v>
+        <v>6343838</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
         <v>118922021</v>
       </c>
       <c r="B22" t="n">
-        <v>108714</v>
+        <v>108721</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>118922042</v>
       </c>
       <c r="B23" t="n">
-        <v>106569</v>
+        <v>106576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118922017</v>
+        <v>118922018</v>
       </c>
       <c r="B2" t="n">
         <v>108721</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555564</v>
+        <v>555849</v>
       </c>
       <c r="R2" t="n">
-        <v>6343805</v>
+        <v>6343838</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922016</v>
+        <v>118922049</v>
       </c>
       <c r="B3" t="n">
-        <v>108721</v>
+        <v>104908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555502</v>
+        <v>555461</v>
       </c>
       <c r="R3" t="n">
-        <v>6343851</v>
+        <v>6343872</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,6 +863,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118922049</v>
+        <v>118922019</v>
       </c>
       <c r="B4" t="n">
-        <v>104908</v>
+        <v>108721</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>340</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555461</v>
+        <v>555459</v>
       </c>
       <c r="R4" t="n">
-        <v>6343872</v>
+        <v>6343786</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -965,11 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118922019</v>
+        <v>118922016</v>
       </c>
       <c r="B5" t="n">
         <v>108721</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555459</v>
+        <v>555502</v>
       </c>
       <c r="R5" t="n">
-        <v>6343786</v>
+        <v>6343851</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118922128</v>
+        <v>118922017</v>
       </c>
       <c r="B6" t="n">
-        <v>106127</v>
+        <v>108721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555457</v>
+        <v>555564</v>
       </c>
       <c r="R6" t="n">
-        <v>6343871</v>
+        <v>6343805</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118922127</v>
+        <v>118922128</v>
       </c>
       <c r="B7" t="n">
         <v>106127</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555417</v>
+        <v>555457</v>
       </c>
       <c r="R7" t="n">
         <v>6343871</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118922018</v>
+        <v>118922127</v>
       </c>
       <c r="B8" t="n">
-        <v>108721</v>
+        <v>106127</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,16 +1308,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555849</v>
+        <v>555417</v>
       </c>
       <c r="R8" t="n">
-        <v>6343838</v>
+        <v>6343871</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118922021</v>
+        <v>118922042</v>
       </c>
       <c r="B22" t="n">
-        <v>108721</v>
+        <v>106576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,20 +3019,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219955</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555154</v>
+        <v>555114</v>
       </c>
       <c r="R22" t="n">
-        <v>6343774</v>
+        <v>6343763</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3093,6 +3093,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3109,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118922042</v>
+        <v>118922021</v>
       </c>
       <c r="B23" t="n">
-        <v>106576</v>
+        <v>108721</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,20 +3126,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219955</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555114</v>
+        <v>555154</v>
       </c>
       <c r="R23" t="n">
-        <v>6343763</v>
+        <v>6343774</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3195,11 +3200,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>3 ex</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,6 +3214,130 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120496411</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57211</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Accipiter gentilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555068</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6343405</v>
+      </c>
+      <c r="S24" t="n">
+        <v>228</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bill Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33827-2021 artfynd.xlsx
+++ b/artfynd/A 33827-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118858021</v>
+        <v>118922042</v>
       </c>
       <c r="B21" t="n">
-        <v>57445</v>
+        <v>106581</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,49 +2899,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>219955</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
+          <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555068</v>
+        <v>555114</v>
       </c>
       <c r="R21" t="n">
-        <v>6343405</v>
+        <v>6343763</v>
       </c>
       <c r="S21" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2965,22 +2957,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,26 +2973,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bill Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118922042</v>
+        <v>118922021</v>
       </c>
       <c r="B22" t="n">
-        <v>106581</v>
+        <v>108726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,20 +3006,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219955</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3047,10 +3034,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555114</v>
+        <v>555154</v>
       </c>
       <c r="R22" t="n">
-        <v>6343763</v>
+        <v>6343774</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3094,11 +3081,6 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>3 ex</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3111,232 +3093,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>118922021</v>
-      </c>
-      <c r="B23" t="n">
-        <v>108726</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220299</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Moråns ravin, Sm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>555154</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6343774</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Högsby</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Fågelfors</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>120496411</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57239</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100001</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Duvhök</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Accipiter gentilis</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Slätmon, Ryningen S  Mörlunda, Sm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>555068</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6343405</v>
-      </c>
-      <c r="S24" t="n">
-        <v>228</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Högsby</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Fågelfors</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Bill Andersson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Bill Andersson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
